--- a/Peliculas.xlsx
+++ b/Peliculas.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saibo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saibo\Desktop\Peliculas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11880"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11880"/>
   </bookViews>
   <sheets>
     <sheet name="Lista de películas" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Lista de películas'!$2:$2</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -1961,8 +1960,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MovieList" displayName="MovieList" ref="B2:P348" totalsRowShown="0" dataDxfId="1">
   <autoFilter ref="B2:P348"/>
-  <sortState ref="B3:P349">
-    <sortCondition ref="M2:M349"/>
+  <sortState ref="B3:P348">
+    <sortCondition ref="M2:M348"/>
   </sortState>
   <tableColumns count="15">
     <tableColumn id="1" name="N. º" dataCellStyle="Normal"/>
